--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -3288,97 +3288,133 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>年级</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>号码</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>主位置</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>可胜任位置</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>惯用脚</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>踢球风格</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>自我介绍</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>照片文件名</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>照片焦点</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>展示状态</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:L2"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <ns0:cols>
+    <ns0:col width="8" customWidth="1" min="1" max="1"/>
+    <ns0:col width="12" customWidth="1" min="2" max="2"/>
+    <ns0:col width="10" customWidth="1" min="3" max="3"/>
+    <ns0:col width="8" customWidth="1" min="4" max="4"/>
+    <ns0:col width="10" customWidth="1" min="5" max="5"/>
+    <ns0:col width="18" customWidth="1" min="6" max="6"/>
+    <ns0:col width="10" customWidth="1" min="7" max="7"/>
+    <ns0:col width="18" customWidth="1" min="8" max="8"/>
+    <ns0:col width="34" customWidth="1" min="9" max="9"/>
+    <ns0:col width="24" customWidth="1" min="10" max="10"/>
+    <ns0:col width="14" customWidth="1" min="11" max="11"/>
+    <ns0:col width="12" customWidth="1" min="12" max="12"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="26" customHeight="1">
+      <ns0:c r="A1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>排序</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>姓名</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>年级</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>号码</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>主位置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>可胜任位置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>惯用脚</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>踢球风格</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>自我介绍</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>照片文件名</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>照片焦点</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>展示状态</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" t="str">
+        <ns0:v>段世添</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" t="str">
+        <ns0:v>中锋</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" t="str">
+        <ns0:v>前腰</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" t="str">
+        <ns0:v>双脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2"/>
+      <ns0:c r="I2" t="str">
+        <ns0:v>改变生康历史的男人要来了</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" t="str">
+        <ns0:v>duanshitian.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L2" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:autoFilter ref="A1:L1"/>
+  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ns0:tableParts count="1">
+    <ns0:tablePart ns1:id="rId1"/>
+  </ns0:tableParts>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -3293,7 +3293,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:L2"/>
+  <ns0:dimension ref="A1:L4"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <ns0:cols>
     <ns0:col width="8" customWidth="1" min="1" max="1"/>
@@ -3405,6 +3405,70 @@
         <ns0:v>50% 50%</ns0:v>
       </ns0:c>
       <ns0:c r="L2" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" t="str">
+        <ns0:v>何梁柱</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" t="n">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" t="str">
+        <ns0:v>中场</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3"/>
+      <ns0:c r="G3" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3"/>
+      <ns0:c r="I3"/>
+      <ns0:c r="J3" t="str">
+        <ns0:v>heliangzhu.png</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="B4" t="str">
+        <ns0:v>肖思博</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" t="n">
+        <ns0:v>33</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" t="str">
+        <ns0:v>后卫</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4"/>
+      <ns0:c r="G4" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4"/>
+      <ns0:c r="I4"/>
+      <ns0:c r="J4" t="str">
+        <ns0:v>xiaosibo.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L4" t="str">
         <ns0:v>展示</ns0:v>
       </ns0:c>
     </ns0:row>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -3293,7 +3293,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:L4"/>
+  <ns0:dimension ref="A1:L6"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <ns0:cols>
     <ns0:col width="8" customWidth="1" min="1" max="1"/>
@@ -3469,6 +3469,72 @@
         <ns0:v>50% 50%</ns0:v>
       </ns0:c>
       <ns0:c r="L4" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="B5" t="str">
+        <ns0:v>凌淇</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" t="n">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" t="str">
+        <ns0:v>中前场</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5"/>
+      <ns0:c r="G5" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5"/>
+      <ns0:c r="I5"/>
+      <ns0:c r="J5" t="str">
+        <ns0:v>lingqi.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K5" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L5" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" t="n">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="B6" t="str">
+        <ns0:v>雷振廷</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" t="n">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" t="str">
+        <ns0:v>后卫</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" t="str">
+        <ns0:v>中场</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6"/>
+      <ns0:c r="I6"/>
+      <ns0:c r="J6" t="str">
+        <ns0:v>leizhenting.png</ns0:v>
+      </ns0:c>
+      <ns0:c r="K6" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L6" t="str">
         <ns0:v>展示</ns0:v>
       </ns0:c>
     </ns0:row>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -3293,7 +3293,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:L6"/>
+  <ns0:dimension ref="A1:L9"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <ns0:cols>
     <ns0:col width="8" customWidth="1" min="1" max="1"/>
@@ -3538,6 +3538,104 @@
         <ns0:v>展示</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" t="str">
+        <ns0:v>蔡照</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" t="str">
+        <ns0:v>边锋</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7"/>
+      <ns0:c r="G7" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7"/>
+      <ns0:c r="I7"/>
+      <ns0:c r="J7" t="str">
+        <ns0:v>caizhao.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L7" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B8" t="str">
+        <ns0:v>喻新旭</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" t="n">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" t="str">
+        <ns0:v>中锋</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" t="str">
+        <ns0:v>后卫</ns0:v>
+      </ns0:c>
+      <ns0:c r="G8" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H8"/>
+      <ns0:c r="I8"/>
+      <ns0:c r="J8" t="str">
+        <ns0:v>yuxinxu.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K8" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L8" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" t="n">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9" t="str">
+        <ns0:v>叶浩</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" t="n">
+        <ns0:v>66</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" t="str">
+        <ns0:v>边锋</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9"/>
+      <ns0:c r="G9" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9"/>
+      <ns0:c r="I9"/>
+      <ns0:c r="J9" t="str">
+        <ns0:v>yehao.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K9" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L9" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:L1"/>
   <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3548,83 +3646,115 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>年级</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>加入赛季</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>身份</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>职责</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>个人介绍</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>照片文件名</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>照片焦点</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>展示状态</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:J2"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col width="8" customWidth="1" min="1" max="1"/>
+    <ns0:col width="12" customWidth="1" min="2" max="2"/>
+    <ns0:col width="10" customWidth="1" min="3" max="3"/>
+    <ns0:col width="14" customWidth="1" min="4" max="4"/>
+    <ns0:col width="14" customWidth="1" min="5" max="5"/>
+    <ns0:col width="46" customWidth="1" min="6" max="6"/>
+    <ns0:col width="38" customWidth="1" min="7" max="7"/>
+    <ns0:col width="26" customWidth="1" min="8" max="8"/>
+    <ns0:col width="14" customWidth="1" min="9" max="9"/>
+    <ns0:col width="12" customWidth="1" min="10" max="10"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="26" customHeight="1">
+      <ns0:c r="A1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>排序</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>姓名</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>年级</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>加入赛季</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>身份</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>职责</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>个人介绍</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>照片文件名</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>照片焦点</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J1" s="13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>展示状态</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" t="str">
+        <ns0:v>陈晗韵</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" t="str">
+        <ns0:v>2026</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" t="str">
+        <ns0:v>宣传经理</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" t="str">
+        <ns0:v>比赛记录、日常事务</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" t="str">
+        <ns0:v>事在人为</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" t="str">
+        <ns0:v>chenhanyun.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:autoFilter ref="A1:J1"/>
+  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ns0:tableParts count="1">
+    <ns0:tablePart ns1:id="rId1"/>
+  </ns0:tableParts>
+</ns0:worksheet>
 </file>
--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -3293,7 +3293,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:L9"/>
+  <ns0:dimension ref="A1:L10"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <ns0:cols>
     <ns0:col width="8" customWidth="1" min="1" max="1"/>
@@ -3636,6 +3636,38 @@
         <ns0:v>展示</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="B10" t="str">
+        <ns0:v>杨锦泰</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" t="str">
+        <ns0:v>中后卫</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10"/>
+      <ns0:c r="G10" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H10"/>
+      <ns0:c r="I10"/>
+      <ns0:c r="J10" t="str">
+        <ns0:v>yangjintai.png</ns0:v>
+      </ns0:c>
+      <ns0:c r="K10" t="str">
+        <ns0:v>50% 0%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L10" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:L1"/>
   <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3651,7 +3683,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:J2"/>
+  <ns0:dimension ref="A1:J3"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <ns0:cols>
     <ns0:col width="8" customWidth="1" min="1" max="1"/>
@@ -3750,6 +3782,36 @@
         <ns0:v>展示</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" t="str">
+        <ns0:v>刘雨莹</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" t="str">
+        <ns0:v>2025级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" t="str">
+        <ns0:v>2026</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" t="str">
+        <ns0:v>球队经理</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3"/>
+      <ns0:c r="G3" t="str">
+        <ns0:v>欢迎加入我们球队，期待成为大家坚实的后盾</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" t="str">
+        <ns0:v>liuyuying.png</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:J1"/>
   <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="统计汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="球员数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="赛事索引" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="赛程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="新生展示" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="球队经理" sheetId="6" state="visible" r:id="rId6"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'球员数据'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'赛事索引'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'赛程'!$A$1:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'新生展示'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'球队经理'!$A$1:$J$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
-</workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:workbookPr/>
+  <ns0:bookViews>
+    <ns0:workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+  </ns0:bookViews>
+  <ns0:sheets>
+    <ns0:sheet name="统计汇总" sheetId="1" state="visible" ns1:id="rId1"/>
+    <ns0:sheet name="球员数据" sheetId="2" state="visible" ns1:id="rId2"/>
+    <ns0:sheet name="赛事索引" sheetId="3" state="visible" ns1:id="rId3"/>
+    <ns0:sheet name="赛程" sheetId="4" state="visible" ns1:id="rId4"/>
+    <ns0:sheet name="新生展示" sheetId="5" state="visible" ns1:id="rId5"/>
+    <ns0:sheet name="球队经理" sheetId="6" state="visible" ns1:id="rId6"/>
+    <ns0:sheet name="通知公告" sheetId="7" ns1:id="rIdNoticeBoard"/>
+  </ns0:sheets>
+  <ns0:definedNames>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'球员数据'!$A$1:$O$18</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'赛事索引'!$A$1:$F$4</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'赛程'!$A$1:$I$12</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'新生展示'!$A$1:$L$1</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'球队经理'!$A$1:$J$1</ns0:definedName>
+  </ns0:definedNames>
+  <ns0:calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+</ns0:workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1284,6 +1285,114 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/notice-board.xml><?xml version="1.0" encoding="utf-8"?>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetFormatPr defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
+    <ns0:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <ns0:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <ns0:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <ns0:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" t="str" s="7">
+        <ns0:v>公告ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" t="str" s="7">
+        <ns0:v>分类</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" t="str" s="7">
+        <ns0:v>发布日期</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" t="str" s="7">
+        <ns0:v>标题</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" t="str" s="7">
+        <ns0:v>摘要</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" t="str" s="7">
+        <ns0:v>正文</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" t="str" s="7">
+        <ns0:v>名单</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" t="str" s="7">
+        <ns0:v>配图</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" t="str" s="7">
+        <ns0:v>图片说明</ns0:v>
+      </ns0:c>
+      <ns0:c r="J1" t="str" s="7">
+        <ns0:v>关联链接</ns0:v>
+      </ns0:c>
+      <ns0:c r="K1" t="str" s="7">
+        <ns0:v>链接文字</ns0:v>
+      </ns0:c>
+      <ns0:c r="L1" t="str" s="7">
+        <ns0:v>发布状态</ns0:v>
+      </ns0:c>
+      <ns0:c r="M1" t="str" s="7">
+        <ns0:v>置顶</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" ht="190" customHeight="1">
+      <ns0:c r="A2" t="str">
+        <ns0:v>welcome-2026</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" t="str">
+        <ns0:v>新人加入</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" t="str">
+        <ns0:v>2026-09-22</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" t="str">
+        <ns0:v>欢迎2026级新队员加入生康足球队</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" t="str">
+        <ns0:v>九位新面孔，带着对足球的热爱加入球队。欢迎你们，一起迎接新赛季。</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" t="str">
+        <ns0:v>2026年9月，生康足球队迎来了新一届队员。截至本次公告，官网已收录九位2026级新队员的资料。
+从第一次见面到并肩上场，期待大家在训练与比赛中熟悉彼此、共同成长。欢迎加入生康足球队！
+新队员资料及照片已上线，大家也可以在自由战术板中选择新队员进行排阵。</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" t="str">
+        <ns0:v>段世添、何梁柱、肖思博、凌淇、雷振廷、蔡照、喻新旭、叶浩、杨锦泰</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" t="str">
+        <ns0:v>assets/photos/newcomer-meetup-2026-09-15.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" t="str">
+        <ns0:v>2026年9月15日 · 新生见面会合影</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" t="str">
+        <ns0:v>#team</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" t="str">
+        <ns0:v>认识新队员</ns0:v>
+      </ns0:c>
+      <ns0:c r="L2" t="str">
+        <ns0:v>发布</ns0:v>
+      </ns0:c>
+      <ns0:c r="M2" t="str">
+        <ns0:v>是</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</ns0:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:sheetPr>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -1388,6 +1388,47 @@
         <ns0:v>是</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="str">
+        <ns0:v>welcome-tianyangyang-2026</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" t="str">
+        <ns0:v>新人加入</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" t="str">
+        <ns0:v>2026-10-01</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" t="str">
+        <ns0:v>欢迎2026级新队员田杨洋加入球队</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" t="str">
+        <ns0:v>田杨洋的球员资料已上线：2026级，22号，惯用右脚。</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" t="str">
+        <ns0:v>欢迎田杨洋加入生康足球队！期待在新赛季一起训练、并肩上场。</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" t="str">
+        <ns0:v>田杨洋</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" t="str">
+        <ns0:v>assets/players/showcase/tianyangyang-640.webp</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" t="str">
+        <ns0:v>田杨洋 · 2026级 · 22号</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" t="str">
+        <ns0:v>#team</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" t="str">
+        <ns0:v>查看球队成员</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" t="str">
+        <ns0:v>发布</ns0:v>
+      </ns0:c>
+      <ns0:c r="M3" t="str">
+        <ns0:v>否</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </ns0:worksheet>
@@ -3402,7 +3443,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:L10"/>
+  <ns0:dimension ref="A1:L11"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <ns0:cols>
     <ns0:col width="8" customWidth="1" min="1" max="1"/>
@@ -3774,6 +3815,36 @@
         <ns0:v>50% 0%</ns0:v>
       </ns0:c>
       <ns0:c r="L10" t="str">
+        <ns0:v>展示</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="B11" t="str">
+        <ns0:v>田杨洋</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" t="str">
+        <ns0:v>2026级</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" t="n">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11"/>
+      <ns0:c r="F11"/>
+      <ns0:c r="G11" t="str">
+        <ns0:v>右脚</ns0:v>
+      </ns0:c>
+      <ns0:c r="H11"/>
+      <ns0:c r="I11"/>
+      <ns0:c r="J11" t="str">
+        <ns0:v>tianyangyang.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="K11" t="str">
+        <ns0:v>50% 50%</ns0:v>
+      </ns0:c>
+      <ns0:c r="L11" t="str">
         <ns0:v>展示</ns0:v>
       </ns0:c>
     </ns0:row>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -1402,7 +1402,7 @@
         <ns0:v>欢迎2026级新队员田杨洋加入球队</ns0:v>
       </ns0:c>
       <ns0:c r="E3" t="str">
-        <ns0:v>田杨洋的球员资料已上线：2026级，22号，惯用右脚。</ns0:v>
+        <ns0:v>田杨洋的球员资料已上线：2026级，22号，后卫，惯用右脚。</ns0:v>
       </ns0:c>
       <ns0:c r="F3" t="str">
         <ns0:v>欢迎田杨洋加入生康足球队！期待在新赛季一起训练、并肩上场。</ns0:v>
@@ -3831,7 +3831,9 @@
       <ns0:c r="D11" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="E11"/>
+      <ns0:c r="E11" t="str">
+        <ns0:v>后卫</ns0:v>
+      </ns0:c>
       <ns0:c r="F11"/>
       <ns0:c r="G11" t="str">
         <ns0:v>右脚</ns0:v>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -1429,6 +1429,60 @@
         <ns0:v>否</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" t="str">
+        <ns0:v>fangda-cup-draw-2026</ns0:v>
+      </ns0:c>
+      <ns0:c r="B4" t="str">
+        <ns0:v>赛事预告</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" t="str">
+        <ns0:v>2026-10-01</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" t="str">
+        <ns0:v>纺大杯抽签结果及赛前注意事项</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" t="str">
+        <ns0:v>生康分入D组，与材料、管理同组。小组赛采用积分制，前两名出线。请全体队员认真阅读赛前须知。</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" t="str">
+        <ns0:v>一、抽签结果
+A组：研究生、经济、南湖联队。
+B组：机械、纺织、微电子。
+C组：计算机、电气、化环。
+D组：材料、生康、管理。
+小组赛采用积分制，各组前两名出线。具体比赛时间待后续公布。
+二、赛前须知（根据老师赛前通知整理）
+1. 统一着装：队服、长袜、护腿板（长板子）。
+2. 球鞋要求：必须穿足球鞋，不允许钢钉、铁钉、长钉，建议穿碎钉。
+3. 换人流程：队内沟通好后，先找第四官员登记；先下后上，在一分钟内完成。下场可从任意位置离场，但上场只能从规定位置进入，否则可能被处罚。
+4. 与裁判沟通：只有佩戴队长袖标的人可以与主裁判沟通，否则可能被处罚。
+5. 特殊情况：无法比赛的院队，须提前24小时告知裁判组安排补赛，否则视为弃赛。
+6. 到场与迟到：比赛前15分钟必须至少有7人到场；迟到15分钟之后不允许上场。
+7. 判罚手势：各位队员须认识直接任意球、间接任意球、边线球等常见判罚手势。
+8. 以哨声为准：球场上一切以主裁判哨声为主；主裁判若没有吹哨，比赛继续正常进行。
+请全体队员提前检查装备，熟悉参赛要求，并留意后续赛程通知。</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" t="str"/>
+      <ns0:c r="H4" t="str">
+        <ns0:v>assets/photos/fangda-cup-draw-2026.jpg</ns0:v>
+      </ns0:c>
+      <ns0:c r="I4" t="str">
+        <ns0:v>本次纺大杯抽签结果（原图）</ns0:v>
+      </ns0:c>
+      <ns0:c r="J4" t="str">
+        <ns0:v>#matches</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" t="str">
+        <ns0:v>查看赛事栏目</ns0:v>
+      </ns0:c>
+      <ns0:c r="L4" t="str">
+        <ns0:v>发布</ns0:v>
+      </ns0:c>
+      <ns0:c r="M4" t="str">
+        <ns0:v>否</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </ns0:worksheet>

--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R74afa97a85394dcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="Re5c70a4ec3c74b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="R58c33247a82b4a9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="Rdc079ad54c0a410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="Rb99dd523ca8e49d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R3e029bf80c404b5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="R9d5802aac4584934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R35a92ff1c3244065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R28094ff160014cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="Rc0a667a59c634ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="R7555f7ead5f840d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="R42e7db26904b41e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R8e98e8f015744f4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="R8a55850f9630432f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -896,8 +896,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="NewcomerShowcase" displayName="NewcomerShowcase" ref="A1:L1" headerRowCount="1">
-  <x:autoFilter ref="A1:L1"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="NewcomerShowcase" displayName="NewcomerShowcase" ref="A1:L13" headerRowCount="1">
+  <x:autoFilter ref="A1:L13"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="排序"/>
     <x:tableColumn id="2" name="姓名"/>
@@ -932,6 +932,27 @@
     <x:tableColumn id="10" name="展示状态"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TeamNotices" displayName="TeamNotices" ref="A1:M8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="公告ID"/>
+    <x:tableColumn id="2" name="分类"/>
+    <x:tableColumn id="3" name="发布日期"/>
+    <x:tableColumn id="4" name="标题"/>
+    <x:tableColumn id="5" name="摘要"/>
+    <x:tableColumn id="6" name="正文"/>
+    <x:tableColumn id="7" name="名单"/>
+    <x:tableColumn id="8" name="配图"/>
+    <x:tableColumn id="9" name="图片说明"/>
+    <x:tableColumn id="10" name="关联链接"/>
+    <x:tableColumn id="11" name="链接文字"/>
+    <x:tableColumn id="12" name="发布状态"/>
+    <x:tableColumn id="13" name="置顶"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -2445,7 +2466,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra29ec2479d8b43ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R780d7f7fa1a74aee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2593,7 +2614,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a14aec5b4d54695"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45396dab5c1541f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3180,7 +3201,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcde03a20a5c4a5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re72fcb1560bb4e0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3773,10 +3794,44 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>方昭炬</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>2026级</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>位置待定</x:v>
+      </x:c>
+      <x:c r="F13" t="str"/>
+      <x:c r="G13" t="str">
+        <x:v>右脚</x:v>
+      </x:c>
+      <x:c r="H13" t="str"/>
+      <x:c r="I13" t="str">
+        <x:v>这几天跟肖思博去看球赛，感觉生康球队非常有实力，关键氛围特别好。</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>fangzhaoju.jpg</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>50% 50%</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>展示</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23aefd10815041b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R014e307d94b24c9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3977,7 +4032,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19c0baeb3a6d48bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc97696b39514a04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4349,7 +4404,139 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>douyin-account-2026</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>球队动态</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>2026-10-17</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>纺大杯首战记录及球队抖音上线</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>10月16日对阵材料学院的比赛档案、照片和球队抖音账号已同步上线。</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>生康足球队官网已更新10月16日十一人制纺大杯对阵材料学院的比赛档案，补充本场5张比赛照片；本场摄影：陈晗韵、刘雨莹。
+比赛详情页已同步2:3比分、4-4-2阵容、刘航宇首发门将、吴全银第50分钟替补登场、进球事件、赛后记和本场MVP段世添。官网个人数据继续按逐场记录自动汇总，重复更新不会重复增加出场次数。
+生康足球队抖音账号正式上线，抖音号：67421116473。比赛录像和球队动态会陆续发布，欢迎大家关注。本场段世添进球的助攻人、对方进球时间和完整比赛录像链接仍待补充。</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>陈晗韵、刘雨莹</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>assets/photos/douyin-account-2026.jpg</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>生康足球队抖音账号主页 · 抖音号 67421116473</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>#match/2026-10-16-eleven-material</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>查看本场比赛档案</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>发布</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>welcome-zhaoweiran-2026</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>新人加入</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>2026-10-21</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>欢迎赵慰冉加入生康足球队</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>欢迎2024级赵慰冉以球队经理身份加入生康足球队，经理资料已同步至官网。</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>生康足球队迎来一位新的球队经理——2024级赵慰冉。
+赵慰冉的经理资料已同步至官网经理栏目，身份为球队经理，个人介绍为“我再想想”。
+欢迎赵慰冉加入生康足球队，期待今后一起记录更多比赛和球队故事。</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>赵慰冉</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>assets/managers/zhaoweiran.jpg</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>赵慰冉 · 2024级 · 球队经理</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>#team</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>查看球队经理</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>发布</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>welcome-fangzhaoju-2026</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>新人加入</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>2026-10-21</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>欢迎方昭炬加入生康足球队</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>2026级新队员方昭炬加入球队：44号，惯用右脚，场上位置待定。</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>生康足球队迎来一位新的2026级队员——方昭炬，球衣号码44号，惯用右脚。
+方昭炬的球员资料和照片已同步至官网新生展示及球队成员栏目。其场上位置目前待定，个人统计将从0开始，并在今后的比赛记录中自动累计。
+欢迎方昭炬加入生康足球队。期待一起训练、看球、比赛，继续感受并融入球队的良好氛围。</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>方昭炬</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>assets/players/showcase/fangzhaoju-640.webp</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>方昭炬 · 2026级 · 44号</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>#team</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>查看球队成员</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>发布</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8432ba7fc4c403d"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R35a92ff1c3244065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R28094ff160014cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="Rc0a667a59c634ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="R7555f7ead5f840d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="R42e7db26904b41e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R8e98e8f015744f4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="R8a55850f9630432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R2c5b554c4d6d4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R1eb719d4c1724adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="R45ac1a176d554a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="Rcb91ad5e5b414d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="Rede4719198774f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R7b77c69007774742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="Rb1081fabbf6748ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="164" formatCode="0.0"/>
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
   <x:fonts count="25">
     <x:font>
@@ -662,7 +663,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -715,6 +716,7 @@
     <x:xf numFmtId="164" fontId="0" fillId="39" borderId="11" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="常规" xfId="0"/>
@@ -878,8 +880,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MatchSchedule" displayName="MatchSchedule" ref="A1:I12" headerRowCount="1">
-  <x:autoFilter ref="A1:I12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MatchSchedule" displayName="MatchSchedule" ref="A1:I13" headerRowCount="1" totalsRowCount="0">
+  <x:autoFilter ref="A1:I13"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="赛季"/>
     <x:tableColumn id="2" name="赛事名称"/>
@@ -936,7 +938,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TeamNotices" displayName="TeamNotices" ref="A1:M8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TeamNotices" displayName="TeamNotices" ref="A1:M9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="公告ID"/>
     <x:tableColumn id="2" name="分类"/>
@@ -1570,10 +1572,8 @@
       <x:c r="A4" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">王伯函</x:t>
-        </x:is>
+      <x:c r="B4" s="14" t="str">
+        <x:v>王伯涵</x:v>
       </x:c>
       <x:c r="C4" s="14" t="inlineStr">
         <x:is>
@@ -2466,7 +2466,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R780d7f7fa1a74aee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3a76e6baccc4ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2614,7 +2614,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45396dab5c1541f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb57cef0b97b14ac0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3198,10 +3198,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>2026-2027</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>十一人制纺大杯</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>管理学院</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>2 : 0</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>win</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>武汉纺织大学足球场</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>周霄旭 19′15″（助攻：段世添） / 段世添 60′（助攻：周霄旭）</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>生康十一人制正式比赛首胜。刘航宇零封，段世添连续第二场当选MVP。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re72fcb1560bb4e0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744a14c972e74f6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3831,7 +3860,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R014e307d94b24c9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9258e5c100044b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3908,10 +3937,8 @@
       <x:c r="A2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">陈晗韵</x:t>
-        </x:is>
+      <x:c r="B2" t="str">
+        <x:v>陈涵韵</x:v>
       </x:c>
       <x:c r="C2" t="inlineStr">
         <x:is>
@@ -4032,7 +4059,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc97696b39514a04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff6f41b809eb4fa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4421,12 +4448,12 @@
         <x:v>10月16日对阵材料学院的比赛档案、照片和球队抖音账号已同步上线。</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>生康足球队官网已更新10月16日十一人制纺大杯对阵材料学院的比赛档案，补充本场5张比赛照片；本场摄影：陈晗韵、刘雨莹。
+        <x:v>生康足球队官网已更新10月16日十一人制纺大杯对阵材料学院的比赛档案，补充本场5张比赛照片；本场摄影：陈涵韵、刘雨莹。
 比赛详情页已同步2:3比分、4-4-2阵容、刘航宇首发门将、吴全银第50分钟替补登场、进球事件、赛后记和本场MVP段世添。官网个人数据继续按逐场记录自动汇总，重复更新不会重复增加出场次数。
 生康足球队抖音账号正式上线，抖音号：67421116473。比赛录像和球队动态会陆续发布，欢迎大家关注。本场段世添进球的助攻人、对方进球时间和完整比赛录像链接仍待补充。</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>陈晗韵、刘雨莹</x:v>
+        <x:v>陈涵韵、刘雨莹</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>assets/photos/douyin-account-2026.jpg</x:v>
@@ -4533,10 +4560,49 @@
         <x:v>是</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>eleven-first-win-management-2026</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>比赛战报</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="d">
+        <x:v>2026-10-24T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>十一人制首胜，生康2:0战胜管理</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>10月23日，生康2:0战胜管理学院，取得球队十一人制正式比赛首胜。</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>10月23日，生康足球队在十一人制纺大杯小组赛中以2:0战胜管理学院，取得球队十一人制正式比赛首胜。半年前的遗憾没有重演，生康终于站在了胜利的一方。
+第19分15秒，段世添助攻周霄旭右脚抽射破门；第60分钟，周霄旭送出助攻，段世添一条龙推进后在禁区外轰出世界波锁定胜局。刘航宇完成零封，段世添连续第二场当选本场MVP。
+完整比分、4-4-2阵容、换人、进球、场外录制和赛后记录已同步至官网，所有出场及个人数据均由本场比赛明细自动累计。本场照片与完整比赛录像暂未收录，后续如有将继续补充。</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>周霄旭、段世添、刘航宇</x:v>
+      </x:c>
+      <x:c r="H9" t="str"/>
+      <x:c r="I9" t="str"/>
+      <x:c r="J9" t="str">
+        <x:v>#match/2026-10-23-eleven-management</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>查看本场比赛档案</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>发布</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8432ba7fc4c403d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec30638b050f44c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R2c5b554c4d6d4a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R1eb719d4c1724adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="R45ac1a176d554a24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="Rcb91ad5e5b414d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="Rede4719198774f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R7b77c69007774742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="Rb1081fabbf6748ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R30208d0fa47c4015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R8246ea459fa94877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="Rba4a12dec90546a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="R5f8f9296210d4682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="Rbd160f1121c144c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R54af17a276b245e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="R0c521b060c294c51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2466,7 +2466,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3a76e6baccc4ec3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47aa03ae40fe4528"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2614,7 +2614,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb57cef0b97b14ac0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb08c6ed2cb2c4a25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3230,7 +3230,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744a14c972e74f6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431ffd38a1f44489"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3860,7 +3860,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9258e5c100044b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb00a4620391a4bdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3938,7 +3938,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>陈涵韵</x:v>
+        <x:v>陈晗韵</x:v>
       </x:c>
       <x:c r="C2" t="inlineStr">
         <x:is>
@@ -4059,7 +4059,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff6f41b809eb4fa9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3964fa63d17c4a81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4448,12 +4448,12 @@
         <x:v>10月16日对阵材料学院的比赛档案、照片和球队抖音账号已同步上线。</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>生康足球队官网已更新10月16日十一人制纺大杯对阵材料学院的比赛档案，补充本场5张比赛照片；本场摄影：陈涵韵、刘雨莹。
+        <x:v>生康足球队官网已更新10月16日十一人制纺大杯对阵材料学院的比赛档案，补充本场5张比赛照片；本场摄影：陈晗韵、刘雨莹。
 比赛详情页已同步2:3比分、4-4-2阵容、刘航宇首发门将、吴全银第50分钟替补登场、进球事件、赛后记和本场MVP段世添。官网个人数据继续按逐场记录自动汇总，重复更新不会重复增加出场次数。
 生康足球队抖音账号正式上线，抖音号：67421116473。比赛录像和球队动态会陆续发布，欢迎大家关注。本场段世添进球的助攻人、对方进球时间和完整比赛录像链接仍待补充。</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>陈涵韵、刘雨莹</x:v>
+        <x:v>陈晗韵、刘雨莹</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>assets/photos/douyin-account-2026.jpg</x:v>
@@ -4599,10 +4599,47 @@
         <x:v>是</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>name-corrections-2026-10-24</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>资料更正</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>2026-10-24</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>人员姓名信息更正</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>官网已统一更正陈晗韵、王恺程两位人员的姓名信息。</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>生康足球队官网已完成两处人员姓名信息更正，正确姓名为陈晗韵、王恺程。
+相关经理资料、10月16日比赛摄影记录、10月23日场外录制记录、公告和数据档案均已同步更新。
+本次更正不影响比赛成绩与球员个人统计，官网现有记录均以更正后的姓名为准。</x:v>
+      </x:c>
+      <x:c r="G10" t="str"/>
+      <x:c r="H10" t="str"/>
+      <x:c r="I10" t="str"/>
+      <x:c r="J10" t="str">
+        <x:v>#matches</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>查看比赛记录</x:v>
+      </x:c>
+      <x:c r="L10" t="str">
+        <x:v>发布</x:v>
+      </x:c>
+      <x:c r="M10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec30638b050f44c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re37b03409f144640"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/生康足球队数据源.xlsx
+++ b/data/生康足球队数据源.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="R30208d0fa47c4015"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R8246ea459fa94877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="Rba4a12dec90546a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="R5f8f9296210d4682"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="Rbd160f1121c144c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R54af17a276b245e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="R0c521b060c294c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="1" r:id="Rcc8effb44ab54727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球员数据" sheetId="2" r:id="R6c9e1bc7932e4ce7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事索引" sheetId="3" r:id="Re95813570b3a4cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛程" sheetId="4" r:id="Rc38638c7ea954589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新生展示" sheetId="5" r:id="R4410d5fb24df4a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="球队经理" sheetId="6" r:id="R4c4bd7b2aab348fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知公告" sheetId="7" r:id="R0ad2463b126d4f91"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2466,7 +2466,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47aa03ae40fe4528"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd592c16c4184bb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2614,7 +2614,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb08c6ed2cb2c4a25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R987590fc505f48f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3230,7 +3230,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431ffd38a1f44489"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32685526b87e4244"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3860,7 +3860,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb00a4620391a4bdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ce21d207b6461c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4059,7 +4059,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3964fa63d17c4a81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6369d6e4f434dda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4600,46 +4600,24 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>name-corrections-2026-10-24</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>资料更正</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>2026-10-24</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>人员姓名信息更正</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>官网已统一更正陈晗韵、王恺程两位人员的姓名信息。</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>生康足球队官网已完成两处人员姓名信息更正，正确姓名为陈晗韵、王恺程。
-相关经理资料、10月16日比赛摄影记录、10月23日场外录制记录、公告和数据档案均已同步更新。
-本次更正不影响比赛成绩与球员个人统计，官网现有记录均以更正后的姓名为准。</x:v>
-      </x:c>
-      <x:c r="G10" t="str"/>
-      <x:c r="H10" t="str"/>
-      <x:c r="I10" t="str"/>
-      <x:c r="J10" t="str">
-        <x:v>#matches</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>查看比赛记录</x:v>
-      </x:c>
-      <x:c r="L10" t="str">
-        <x:v>发布</x:v>
-      </x:c>
-      <x:c r="M10" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10" s="18"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+      <x:c r="M10"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re37b03409f144640"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00bdbf8d24184d4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>